--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1105,20 +1105,14 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Pramod Sapkota</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1133,10 +1127,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9841509605</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9841509605</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1153,10 +1145,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.672256</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.672256</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1212,25 +1202,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.373051</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.373051</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1331,10 +1317,8 @@
           <t>Saman Lamichhane</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9813824865</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9813824865</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1349,10 +1333,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9813824865</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9813824865</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1369,10 +1351,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.676466</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.676466</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1424,25 +1404,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L3-4</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.363121</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.36312100000001</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -639,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -666,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -700,8 +724,11 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>1</v>
+      <c r="C2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +740,10 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -728,6 +758,9 @@
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -741,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -771,7 +804,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -787,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1452,6 +1485,434 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 1:05 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375301</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Kishor Shrestha</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Kishor Shrestha</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9851060333</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9818332206</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 11:41:51 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:05:41 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.69469</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Next to Agni Motoinc Pvt. Ltd, Teku, kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>kishor9851060333@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>11:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB043</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.30412</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 23m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 1:04 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375528</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Ram Khadka</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bhola Ram Khadka</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9801055714</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9851037495</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 07:43:24 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:04:18 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.758847</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, Q85W+7VJ, ??????????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>03:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.346056</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>17h 20m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_21_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1552,10 +1552,8 @@
           <t>Kishor Shrestha</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9851060333</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9851060333</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1570,10 +1568,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9818332206</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9818332206</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1590,10 +1586,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.69469</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.69469</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1649,25 +1643,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB043</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.30412</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.30412</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1768,10 +1758,8 @@
           <t>Bhola Ram Khadka</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9801055714</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9801055714</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1786,10 +1774,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9851037495</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9851037495</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1806,10 +1792,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.758847</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.758847</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1861,25 +1845,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L36-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.346056</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.346056</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
